--- a/222/222_222/007_BKU3/条件输入数据表.xlsx
+++ b/222/222_222/007_BKU3/条件输入数据表.xlsx
@@ -1822,8 +1822,16 @@
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr"/>
-      <c r="D3" s="8" t="inlineStr"/>
-      <c r="E3" s="25" t="inlineStr"/>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>轻度</t>
+        </is>
+      </c>
+      <c r="E3" s="25" t="inlineStr">
+        <is>
+          <t>轻度</t>
+        </is>
+      </c>
       <c r="G3" s="24" t="inlineStr">
         <is>
           <t>设计压力*</t>
@@ -1851,8 +1859,16 @@
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr"/>
-      <c r="D4" s="8" t="inlineStr"/>
-      <c r="E4" s="25" t="inlineStr"/>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>易爆</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="inlineStr">
+        <is>
+          <t>易爆</t>
+        </is>
+      </c>
       <c r="G4" s="24" t="inlineStr">
         <is>
           <t>设计温度（最高）*</t>
@@ -1880,8 +1896,16 @@
         </is>
       </c>
       <c r="C5" s="33" t="inlineStr"/>
-      <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="25" t="inlineStr"/>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>液化气体</t>
+        </is>
+      </c>
+      <c r="E5" s="25" t="inlineStr">
+        <is>
+          <t>液化气体</t>
+        </is>
+      </c>
       <c r="G5" s="24" t="inlineStr">
         <is>
           <t>工作压力</t>
